--- a/MinMax/scripts/comparison/violations_comparison_table_57_2.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_57_2.xlsx
@@ -465,10 +465,10 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0.1174418553709984</v>
+        <v>0.1172144263982773</v>
       </c>
       <c r="E2">
-        <v>0.03003126382827759</v>
+        <v>0.03447685018181801</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -482,10 +482,10 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.5197469592094421</v>
+        <v>0.5317502617835999</v>
       </c>
       <c r="E3">
-        <v>0.1726090908050537</v>
+        <v>0.2102972269058228</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -496,13 +496,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.001282383222132921</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.003306403756141663</v>
+        <v>0.003890617517754436</v>
       </c>
       <c r="E4">
-        <v>0.06273507326841354</v>
+        <v>0.06883388757705688</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.01538859866559505</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.02037584781646729</v>
+        <v>0.05175966024398804</v>
       </c>
       <c r="E5">
-        <v>0.3411948680877686</v>
+        <v>0.5982745885848999</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.002102966187521815</v>
+        <v>0.004984830506145954</v>
       </c>
       <c r="E6">
-        <v>0.02997169829905033</v>
+        <v>0.03953883424401283</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.01386252045631409</v>
+        <v>0.1663174033164978</v>
       </c>
       <c r="E7">
-        <v>0.2052476406097412</v>
+        <v>0.5815850496292114</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>5.029429303249344E-05</v>
+        <v>5.028838131693192E-05</v>
       </c>
       <c r="C12">
-        <v>5.029690873925574E-05</v>
+        <v>5.029184103477746E-05</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.002868413925170898</v>
+        <v>0.0028725266456604</v>
       </c>
       <c r="C13">
-        <v>0.002868294715881348</v>
+        <v>0.002872943878173828</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>1.736385927764947E-08</v>
+        <v>1.519115697065959E-08</v>
       </c>
       <c r="C16">
-        <v>1.321954542404788E-08</v>
+        <v>2.051496940630535E-08</v>
       </c>
       <c r="D16">
-        <v>1.455552714288886E-06</v>
+        <v>1.080407741937961E-06</v>
       </c>
       <c r="E16">
-        <v>1.498329133879737E-06</v>
+        <v>1.187271323033201E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>3.690961667613194E-07</v>
+        <v>4.107542282674319E-07</v>
       </c>
       <c r="C17">
-        <v>2.745535275431601E-07</v>
+        <v>3.768421927427308E-07</v>
       </c>
       <c r="D17">
-        <v>6.574908367699469E-06</v>
+        <v>6.574908184120432E-06</v>
       </c>
       <c r="E17">
-        <v>7.803429531599589E-06</v>
+        <v>8.207175596908201E-06</v>
       </c>
     </row>
   </sheetData>
